--- a/data/trans_bre/P05A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P05A_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-9,64%</t>
+          <t>-6,03%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 6,6</t>
+          <t>-1,05; 6,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 5,19</t>
+          <t>-3,08; 5,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 2,3</t>
+          <t>-7,06; 2,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 1,82</t>
+          <t>-5,28; 2,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 22,3</t>
+          <t>-2,93; 23,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 14,48</t>
+          <t>-7,59; 15,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 6,98</t>
+          <t>-17,8; 7,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 10,87</t>
+          <t>-23,63; 13,99</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,05</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 10,66</t>
+          <t>4,21; 10,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 3,03</t>
+          <t>-3,59; 2,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 4,91</t>
+          <t>-1,32; 4,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 29,73</t>
+          <t>0,62; 5,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,59; 41,29</t>
+          <t>14,15; 41,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 8,17</t>
+          <t>-8,83; 7,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 14,8</t>
+          <t>-3,69; 14,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,43; 238,67</t>
+          <t>3,18; 33,27</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 6,49</t>
+          <t>-5,22; 6,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 6,72</t>
+          <t>-6,49; 6,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 6,85</t>
+          <t>-5,42; 6,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 5,59</t>
+          <t>-3,41; 5,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 21,13</t>
+          <t>-14,77; 22,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 16,8</t>
+          <t>-13,62; 15,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 18,91</t>
+          <t>-12,37; 17,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 27,82</t>
+          <t>-13,77; 29,04</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,71</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,11</t>
+          <t>2,5; 6,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,4</t>
+          <t>-2,2; 2,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,92</t>
+          <t>-1,77; 3,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 21,69</t>
+          <t>0,01; 3,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,4; 25,16</t>
+          <t>8,29; 24,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 6,2</t>
+          <t>-5,3; 6,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 8,44</t>
+          <t>-4,75; 9,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 150,63</t>
+          <t>0,07; 21,84</t>
         </is>
       </c>
     </row>
